--- a/data/trans_bre/IP12-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 6,77</t>
+          <t>-12,5; 6,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 5,88</t>
+          <t>-13,98; 5,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 11,45</t>
+          <t>-11,31; 10,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 5,84</t>
+          <t>-5,81; 6,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,36; 82,71</t>
+          <t>-68,13; 93,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-76,05; 90,34</t>
+          <t>-77,82; 78,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-52,64; 120,22</t>
+          <t>-53,38; 109,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-87,11; 683,9</t>
+          <t>-97,96; 470,04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 10,7</t>
+          <t>-0,52; 10,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 5,84</t>
+          <t>-8,04; 5,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 8,18</t>
+          <t>-3,87; 8,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 7,86</t>
+          <t>-5,65; 7,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 392,56</t>
+          <t>-15,6; 332,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,3; 66,16</t>
+          <t>-49,44; 61,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,95; 179,62</t>
+          <t>-42,75; 199,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,3; 210,96</t>
+          <t>-58,01; 193,45</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 6,47</t>
+          <t>-5,04; 6,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 10,05</t>
+          <t>-6,96; 10,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 6,67</t>
+          <t>-2,75; 6,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 11,67</t>
+          <t>-6,92; 10,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-80,79; 542,94</t>
+          <t>-81,09; 407,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,94; 174,48</t>
+          <t>-52,8; 193,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 254,52</t>
+          <t>-57,09; 208,86</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 5,52</t>
+          <t>-10,23; 5,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 11,0</t>
+          <t>-4,49; 10,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 8,78</t>
+          <t>-8,28; 8,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 5,13</t>
+          <t>-15,22; 5,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,44; 86,8</t>
+          <t>-70,28; 76,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,88; 255,88</t>
+          <t>-43,19; 258,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,56; 106,76</t>
+          <t>-51,3; 110,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,73; 160,75</t>
+          <t>-88,98; 150,31</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 8,28</t>
+          <t>-2,97; 8,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 18,61</t>
+          <t>-7,44; 18,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 17,19</t>
+          <t>-0,98; 16,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 12,74</t>
+          <t>-5,83; 13,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,24 +1085,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,2; 226,24</t>
+          <t>-41,32; 247,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-51,54; 1322,3</t>
+          <t>-46,49; 1165,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-62,85; 428,61</t>
+          <t>-62,42; 522,85</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 8,56</t>
+          <t>-4,95; 9,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 9,37</t>
+          <t>-7,12; 9,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 2,34</t>
+          <t>-8,71; 2,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,15; 1,01</t>
+          <t>-18,14; 1,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,03; 356,4</t>
+          <t>-70,71; 442,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,91; 218,85</t>
+          <t>-63,0; 275,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,14 +1195,14 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,13; 22,1</t>
+          <t>-80,15; 21,92</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 7,42</t>
+          <t>-0,69; 7,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 4,72</t>
+          <t>-3,3; 5,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 4,48</t>
+          <t>-2,81; 4,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 7,16</t>
+          <t>-5,3; 6,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,81; 542,02</t>
+          <t>-28,05; 543,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-59,32; 222,94</t>
+          <t>-58,76; 214,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-61,59; 275,13</t>
+          <t>-60,07; 291,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-44,2; 118,52</t>
+          <t>-44,36; 116,29</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,53; -1,11</t>
+          <t>-9,6; -1,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 1,6</t>
+          <t>-5,67; 2,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 7,14</t>
+          <t>-1,9; 6,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 0,65</t>
+          <t>-6,64; 0,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-81,89; -13,56</t>
+          <t>-80,45; -11,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,57; 47,88</t>
+          <t>-70,76; 52,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 193,94</t>
+          <t>-26,62; 171,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-82,3; 28,4</t>
+          <t>-79,75; 50,59</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,92</t>
+          <t>-2,15; 2,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,66</t>
+          <t>-2,3; 2,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,59</t>
+          <t>-0,92; 3,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,02</t>
+          <t>-3,41; 1,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 34,59</t>
+          <t>-29,14; 37,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 38,39</t>
+          <t>-24,42; 35,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 66,05</t>
+          <t>-13,28; 69,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-33,8; 31,32</t>
+          <t>-37,01; 24,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP12-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 6,87</t>
+          <t>-11,46; 8,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 5,16</t>
+          <t>-13,55; 6,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 10,79</t>
+          <t>-10,98; 11,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 6,04</t>
+          <t>-5,61; 6,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,13; 93,96</t>
+          <t>-65,62; 102,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-77,82; 78,37</t>
+          <t>-76,71; 101,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,38; 109,46</t>
+          <t>-53,42; 109,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-97,96; 470,04</t>
+          <t>-87,18; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 10,8</t>
+          <t>-0,94; 10,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 5,92</t>
+          <t>-7,86; 6,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 8,51</t>
+          <t>-3,46; 8,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 7,5</t>
+          <t>-5,2; 7,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 332,73</t>
+          <t>-15,09; 360,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,44; 61,86</t>
+          <t>-50,68; 76,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,75; 199,23</t>
+          <t>-38,39; 183,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,01; 193,45</t>
+          <t>-55,37; 201,65</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 6,13</t>
+          <t>-5,37; 6,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 10,81</t>
+          <t>-7,68; 10,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 6,55</t>
+          <t>-2,63; 6,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 10,84</t>
+          <t>-5,29; 11,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-81,09; 407,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-52,8; 193,36</t>
+          <t>-56,33; 166,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-57,09; 208,86</t>
+          <t>-46,22; 298,02</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 5,02</t>
+          <t>-9,21; 5,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 10,97</t>
+          <t>-4,72; 11,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 8,91</t>
+          <t>-8,51; 10,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 5,01</t>
+          <t>-14,59; 5,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,28; 76,15</t>
+          <t>-65,61; 85,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,19; 258,21</t>
+          <t>-40,16; 295,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,3; 110,88</t>
+          <t>-52,26; 122,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-88,98; 150,31</t>
+          <t>-88,44; 162,01</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 8,04</t>
+          <t>-2,96; 8,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 18,73</t>
+          <t>-7,41; 17,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 16,84</t>
+          <t>-0,79; 16,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 13,23</t>
+          <t>-5,17; 13,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 247,5</t>
+          <t>-40,97; 228,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-46,49; 1165,67</t>
+          <t>-43,17; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-62,42; 522,85</t>
+          <t>-57,56; 429,2</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 9,14</t>
+          <t>-6,03; 8,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 9,69</t>
+          <t>-7,92; 10,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 2,13</t>
+          <t>-8,05; 1,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 1,74</t>
+          <t>-19,19; 0,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,71; 442,46</t>
+          <t>-79,79; 366,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,0; 275,83</t>
+          <t>-71,61; 255,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,15; 21,92</t>
+          <t>-81,68; 15,44</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 7,75</t>
+          <t>-1,07; 7,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 5,07</t>
+          <t>-3,65; 4,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 4,62</t>
+          <t>-2,8; 4,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 6,86</t>
+          <t>-5,24; 7,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 543,4</t>
+          <t>-29,97; 588,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-58,76; 214,4</t>
+          <t>-59,82; 214,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-60,07; 291,75</t>
+          <t>-63,59; 285,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-44,36; 116,29</t>
+          <t>-45,76; 119,75</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,6; -1,15</t>
+          <t>-10,2; -1,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 2,03</t>
+          <t>-5,67; 1,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 6,92</t>
+          <t>-1,96; 6,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 0,9</t>
+          <t>-6,47; 0,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-80,45; -11,52</t>
+          <t>-83,57; -14,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,76; 52,51</t>
+          <t>-68,6; 56,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 171,67</t>
+          <t>-29,97; 153,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-79,75; 50,59</t>
+          <t>-79,93; 37,31</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,2</t>
+          <t>-2,13; 2,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 2,58</t>
+          <t>-2,32; 2,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,61</t>
+          <t>-0,75; 3,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,66</t>
+          <t>-3,1; 1,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 37,08</t>
+          <t>-28,68; 39,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 35,66</t>
+          <t>-24,44; 34,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 69,14</t>
+          <t>-9,82; 68,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-37,01; 24,54</t>
+          <t>-35,27; 23,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP12-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 8,53</t>
+          <t>-12,3; 6,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 6,2</t>
+          <t>-13,27; 5,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 11,01</t>
+          <t>-11,29; 11,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 6,68</t>
+          <t>-5,73; 7,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-65,62; 102,45</t>
+          <t>-68,36; 82,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-76,71; 101,08</t>
+          <t>-76,05; 90,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,42; 109,65</t>
+          <t>-52,64; 120,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-87,18; —</t>
+          <t>-85,69; 730,32</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>3,79</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>64,13%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 10,96</t>
+          <t>-0,98; 10,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 6,55</t>
+          <t>-8,71; 5,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 8,48</t>
+          <t>-4,19; 8,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 7,52</t>
+          <t>-1,91; 10,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 360,73</t>
+          <t>-19,56; 392,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,68; 76,69</t>
+          <t>-53,3; 66,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,39; 183,16</t>
+          <t>-48,95; 179,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,37; 201,65</t>
+          <t>-30,93; 284,82</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>2,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 6,17</t>
+          <t>-4,89; 6,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 10,19</t>
+          <t>-7,08; 10,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 6,35</t>
+          <t>-2,88; 6,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 11,26</t>
+          <t>-6,96; 11,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>-80,79; 542,94</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-48,94; 174,48</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-56,33; 166,56</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 298,02</t>
+          <t>-59,92; 235,15</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,94</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-33,54%</t>
+          <t>-32,68%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 5,34</t>
+          <t>-8,97; 5,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 11,69</t>
+          <t>-4,36; 11,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 10,05</t>
+          <t>-8,44; 8,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 5,19</t>
+          <t>-14,47; 5,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,61; 85,19</t>
+          <t>-64,44; 86,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,16; 295,75</t>
+          <t>-41,88; 255,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,26; 122,04</t>
+          <t>-48,56; 106,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-88,44; 162,01</t>
+          <t>-85,12; 168,33</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 8,2</t>
+          <t>-2,74; 8,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 17,81</t>
+          <t>-6,27; 18,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 16,37</t>
+          <t>-0,98; 17,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 13,79</t>
+          <t>-6,8; 12,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,97; 228,66</t>
+          <t>-40,2; 226,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-43,17; —</t>
+          <t>-51,54; 1322,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-57,56; 429,2</t>
+          <t>-63,91; 416,17</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-8,91</t>
+          <t>-8,81</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-49,87%</t>
+          <t>-49,67%</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 8,64</t>
+          <t>-5,41; 8,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 10,21</t>
+          <t>-7,52; 9,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 1,85</t>
+          <t>-7,97; 2,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 0,66</t>
+          <t>-19,39; 1,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,79; 366,84</t>
+          <t>-76,03; 356,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,61; 255,09</t>
+          <t>-64,91; 218,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,68; 15,44</t>
+          <t>-81,26; 17,18</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 7,16</t>
+          <t>-0,88; 7,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 4,91</t>
+          <t>-3,42; 4,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 4,51</t>
+          <t>-2,96; 4,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 7,12</t>
+          <t>-6,44; 6,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,97; 588,42</t>
+          <t>-34,81; 542,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-59,82; 214,87</t>
+          <t>-59,32; 222,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-63,59; 285,82</t>
+          <t>-61,59; 275,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-45,76; 119,75</t>
+          <t>-47,94; 113,13</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-2,55</t>
+          <t>-3,01</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-45,71%</t>
+          <t>-55,03%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,2; -1,06</t>
+          <t>-9,53; -1,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 1,81</t>
+          <t>-6,04; 1,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 6,73</t>
+          <t>-2,14; 7,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 0,74</t>
+          <t>-7,09; -0,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-83,57; -14,68</t>
+          <t>-81,89; -13,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,6; 56,34</t>
+          <t>-70,57; 47,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,97; 153,32</t>
+          <t>-27,39; 193,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-79,93; 37,31</t>
+          <t>-85,72; 9,84</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-8,4%</t>
+          <t>-6,16%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,07</t>
+          <t>-2,21; 1,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,55</t>
+          <t>-2,15; 2,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,63</t>
+          <t>-0,75; 3,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 1,47</t>
+          <t>-3,06; 2,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 39,18</t>
+          <t>-29,64; 34,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 34,03</t>
+          <t>-22,12; 38,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 68,11</t>
+          <t>-10,04; 66,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 23,05</t>
+          <t>-33,67; 32,26</t>
         </is>
       </c>
     </row>
